--- a/data/trans_orig/P14B23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2012</t>
+          <t>Población cuya depresión o ansiedad le limita en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450832</t>
+          <t>450275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424249</t>
+          <t>423231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>876793</t>
+          <t>875766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883561</t>
+          <t>883556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34336</t>
+          <t>32980</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>676315</t>
+          <t>675609</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685201</t>
+          <t>685180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>583152</t>
+          <t>583477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>600508</t>
+          <t>600636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1263006</t>
+          <t>1264362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1283218</t>
+          <t>1284236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37611</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34417</t>
+          <t>34788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>62473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56190</t>
+          <t>55786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91737</t>
+          <t>89247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644252</t>
+          <t>644642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666651</t>
+          <t>666259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644861</t>
+          <t>645235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>673291</t>
+          <t>672920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1297834</t>
+          <t>1300324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1333381</t>
+          <t>1333785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>25872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34309</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60999</t>
+          <t>61819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47826</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81052</t>
+          <t>79439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588375</t>
+          <t>588745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>605617</t>
+          <t>606144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>551100</t>
+          <t>550280</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>577790</t>
+          <t>576375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1145664</t>
+          <t>1147277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1178890</t>
+          <t>1180066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28056</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46124</t>
+          <t>46268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75592</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62857</t>
+          <t>63435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97364</t>
+          <t>97727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401373</t>
+          <t>400967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418098</t>
+          <t>418239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>371252</t>
+          <t>370579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>400720</t>
+          <t>400576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>778909</t>
+          <t>778546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>813416</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>40178</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67159</t>
+          <t>66907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50442</t>
+          <t>50378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81494</t>
+          <t>80756</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288375</t>
+          <t>288538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302698</t>
+          <t>302581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>286837</t>
+          <t>287089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313450</t>
+          <t>313818</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>581190</t>
+          <t>581928</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>612242</t>
+          <t>612306</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46340</t>
+          <t>46149</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76576</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53916</t>
+          <t>52314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86175</t>
+          <t>84622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229553</t>
+          <t>230235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244667</t>
+          <t>244584</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309254</t>
+          <t>310856</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339490</t>
+          <t>339681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>548456</t>
+          <t>550009</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>580715</t>
+          <t>582317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68163</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107992</t>
+          <t>107473</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>253008</t>
+          <t>251793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>319642</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>333642</t>
+          <t>336930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>406157</t>
+          <t>414637</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3316638</t>
+          <t>3317157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3356467</t>
+          <t>3356974</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3227321</t>
+          <t>3229130</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3293955</t>
+          <t>3295170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6565435</t>
+          <t>6556955</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6637950</t>
+          <t>6634662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2016</t>
+          <t>Población cuya depresión o ansiedad le limita en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411473</t>
+          <t>411548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377152</t>
+          <t>377501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391158</t>
+          <t>391805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794916</t>
+          <t>793409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>809546</t>
+          <t>809194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>13488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584681</t>
+          <t>582833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>550701</t>
+          <t>550056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>560801</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1139041</t>
+          <t>1138200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150319</t>
+          <t>1150273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>17825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36304</t>
+          <t>37207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26741</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50272</t>
+          <t>49892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>649669</t>
+          <t>649866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663379</t>
+          <t>663507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625082</t>
+          <t>624179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643542</t>
+          <t>643561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1280211</t>
+          <t>1280591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1303742</t>
+          <t>1303466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29304</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66108</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88553</t>
+          <t>87135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616744</t>
+          <t>616105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>633826</t>
+          <t>634658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582969</t>
+          <t>582189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611404</t>
+          <t>610646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1206572</t>
+          <t>1207990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1240463</t>
+          <t>1240185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43952</t>
+          <t>42509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72741</t>
+          <t>71580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58200</t>
+          <t>58386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92207</t>
+          <t>94837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449533</t>
+          <t>449601</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467266</t>
+          <t>467357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424108</t>
+          <t>425269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>452897</t>
+          <t>454340</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>882560</t>
+          <t>879930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916567</t>
+          <t>916381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31372</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56185</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>34857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61662</t>
+          <t>61741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>325473</t>
+          <t>325407</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333403</t>
+          <t>333394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>321577</t>
+          <t>320903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346390</t>
+          <t>345754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>650430</t>
+          <t>650351</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>676954</t>
+          <t>677235</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34837</t>
+          <t>33353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63700</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>41249</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73224</t>
+          <t>72948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>240273</t>
+          <t>241058</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251355</t>
+          <t>251983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>336469</t>
+          <t>337895</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>365332</t>
+          <t>366816</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>583943</t>
+          <t>584219</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>615102</t>
+          <t>615918</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53009</t>
+          <t>51745</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>208193</t>
+          <t>206790</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>268155</t>
+          <t>268244</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270864</t>
+          <t>273416</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>340407</t>
+          <t>340593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3309139</t>
+          <t>3309984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3341341</t>
+          <t>3342605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3276387</t>
+          <t>3276298</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3336349</t>
+          <t>3337752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6598485</t>
+          <t>6598299</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6668028</t>
+          <t>6665476</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2023</t>
+          <t>Población cuya depresión o ansiedad le limita en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23780</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25464</t>
+          <t>25332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376207</t>
+          <t>372657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397525</t>
+          <t>397044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287736</t>
+          <t>287868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307568</t>
+          <t>308262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>675341</t>
+          <t>674915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>702224</t>
+          <t>702656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,47 +7048,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>20185</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11604</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32185</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20185</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10205</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>31048</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36913</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413916</t>
+          <t>414261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422497</t>
+          <t>422436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,49 +7161,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>491908</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>479908</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>500489</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,71%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>97,73%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>491908</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>481045</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>501888</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>739</t>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>898727</t>
+          <t>899267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920441</t>
+          <t>920874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>34183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36900</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>37669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63582</t>
+          <t>65107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501509</t>
+          <t>502155</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521985</t>
+          <t>521993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>555102</t>
+          <t>555943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573039</t>
+          <t>573954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1064758</t>
+          <t>1063233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1091321</t>
+          <t>1090671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52302</t>
+          <t>51137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45409</t>
+          <t>44904</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69883</t>
+          <t>69752</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52849</t>
+          <t>56651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114149</t>
+          <t>116099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>835484</t>
+          <t>836649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873546</t>
+          <t>873296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642998</t>
+          <t>643129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>667977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1486518</t>
+          <t>1484568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1547818</t>
+          <t>1544016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
+          <t>43630</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53186</t>
+          <t>53420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75632</t>
+          <t>75787</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81670</t>
+          <t>80031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112380</t>
+          <t>112127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>517820</t>
+          <t>517604</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538295</t>
+          <t>538075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472273</t>
+          <t>472118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>494719</t>
+          <t>494485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996759</t>
+          <t>997012</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1027469</t>
+          <t>1029108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66828</t>
+          <t>67142</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>26088</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71833</t>
+          <t>71841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>350607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361469</t>
+          <t>361501</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>541540</t>
+          <t>541226</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>591374</t>
+          <t>591345</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>904700</t>
+          <t>904692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>947901</t>
+          <t>950445</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>37908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56528</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50276</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73422</t>
+          <t>73221</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>261131</t>
+          <t>261761</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273777</t>
+          <t>273434</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>369303</t>
+          <t>369534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387246</t>
+          <t>387923</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635168</t>
+          <t>635369</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>658314</t>
+          <t>658335</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97311</t>
+          <t>95568</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153069</t>
+          <t>151131</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214393</t>
+          <t>217540</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>300328</t>
+          <t>301198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>344408</t>
+          <t>345309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>437020</t>
+          <t>440752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3306748</t>
+          <t>3308686</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3362506</t>
+          <t>3364249</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3411952</t>
+          <t>3411082</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3497887</t>
+          <t>3494740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6735077</t>
+          <t>6731345</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6827689</t>
+          <t>6826788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P14B23-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Edad-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450275</t>
+          <t>449810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423231</t>
+          <t>424230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875766</t>
+          <t>877081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883556</t>
+          <t>883559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26778</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32980</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>675609</t>
+          <t>676304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685180</t>
+          <t>685186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>583477</t>
+          <t>582921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>600636</t>
+          <t>600395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1264362</t>
+          <t>1262819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1284236</t>
+          <t>1283314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>36936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>36202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62473</t>
+          <t>62678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55786</t>
+          <t>56049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89247</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644642</t>
+          <t>644927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666259</t>
+          <t>667352</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645235</t>
+          <t>645030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672920</t>
+          <t>671506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300324</t>
+          <t>1299316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1333785</t>
+          <t>1333522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>35013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61819</t>
+          <t>62197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46650</t>
+          <t>47615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79439</t>
+          <t>79748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588745</t>
+          <t>589066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>606144</t>
+          <t>605585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550280</t>
+          <t>549902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>576375</t>
+          <t>577086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1147277</t>
+          <t>1146968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1180066</t>
+          <t>1179101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46268</t>
+          <t>45849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76265</t>
+          <t>74011</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63435</t>
+          <t>61148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97727</t>
+          <t>96103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400967</t>
+          <t>400836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418239</t>
+          <t>417744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370579</t>
+          <t>372833</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>400576</t>
+          <t>400995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>778546</t>
+          <t>780170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>815125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40178</t>
+          <t>39447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66907</t>
+          <t>66215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50378</t>
+          <t>49647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80756</t>
+          <t>81016</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288538</t>
+          <t>287842</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302581</t>
+          <t>303441</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>287089</t>
+          <t>287781</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313818</t>
+          <t>314549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>581928</t>
+          <t>581668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>612306</t>
+          <t>613037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46149</t>
+          <t>45803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74974</t>
+          <t>73176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>53011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84622</t>
+          <t>86549</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230235</t>
+          <t>230609</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244584</t>
+          <t>244492</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310856</t>
+          <t>312654</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339681</t>
+          <t>340027</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>550009</t>
+          <t>548082</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>582317</t>
+          <t>581620</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67656</t>
+          <t>69133</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107473</t>
+          <t>108333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>251793</t>
+          <t>255069</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>317833</t>
+          <t>317908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>336930</t>
+          <t>334280</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>414637</t>
+          <t>407596</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3317157</t>
+          <t>3316297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3356974</t>
+          <t>3355497</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3229130</t>
+          <t>3229055</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3295170</t>
+          <t>3291894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6556955</t>
+          <t>6563996</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6634662</t>
+          <t>6637312</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411548</t>
+          <t>411946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377501</t>
+          <t>378790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391805</t>
+          <t>391741</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>793409</t>
+          <t>793752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>809194</t>
+          <t>809448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>582833</t>
+          <t>583740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>550056</t>
+          <t>551061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>561592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1138200</t>
+          <t>1138038</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150273</t>
+          <t>1150255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37207</t>
+          <t>35959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>649866</t>
+          <t>649546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663507</t>
+          <t>663729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624179</t>
+          <t>625427</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643561</t>
+          <t>643226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1280591</t>
+          <t>1279526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1303466</t>
+          <t>1303587</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66888</t>
+          <t>65456</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>55146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87135</t>
+          <t>87889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616105</t>
+          <t>616913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>634658</t>
+          <t>633832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582189</t>
+          <t>583621</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610646</t>
+          <t>611291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207990</t>
+          <t>1207236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1240185</t>
+          <t>1239979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42509</t>
+          <t>43796</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71580</t>
+          <t>71396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>57566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>92397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449601</t>
+          <t>449456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467357</t>
+          <t>466917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>425269</t>
+          <t>425453</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454340</t>
+          <t>453053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>879930</t>
+          <t>882370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916381</t>
+          <t>917201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>56986</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34857</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61741</t>
+          <t>62421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>325407</t>
+          <t>325357</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333394</t>
+          <t>333313</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>320903</t>
+          <t>320776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345754</t>
+          <t>345369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>650351</t>
+          <t>649671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>677235</t>
+          <t>676903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62274</t>
+          <t>61865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41249</t>
+          <t>42145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72948</t>
+          <t>72898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>241058</t>
+          <t>240419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251983</t>
+          <t>251196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337895</t>
+          <t>338304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>366816</t>
+          <t>366702</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>584219</t>
+          <t>584269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>615918</t>
+          <t>615022</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51745</t>
+          <t>51778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84366</t>
+          <t>86034</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>206790</t>
+          <t>207921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>268244</t>
+          <t>270549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>273416</t>
+          <t>271816</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>340593</t>
+          <t>345097</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3309984</t>
+          <t>3308316</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3342605</t>
+          <t>3342572</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3276298</t>
+          <t>3273993</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3337752</t>
+          <t>3336621</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6598299</t>
+          <t>6593795</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6665476</t>
+          <t>6667076</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6685,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6720,32 +6720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,32 +6755,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>37199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -6798,32 +6798,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>391233</t>
+          <t>399193</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372657</t>
+          <t>386881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397044</t>
+          <t>405274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6833,32 +6833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>300839</t>
+          <t>349625</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287868</t>
+          <t>337501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308262</t>
+          <t>357040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6868,32 +6868,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>692072</t>
+          <t>748818</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674915</t>
+          <t>733106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>702656</t>
+          <t>759479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,32 +7028,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,32 +7063,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>35195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>29585</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -7141,32 +7141,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>419956</t>
+          <t>469903</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414261</t>
+          <t>460101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422436</t>
+          <t>474328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7176,32 +7176,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>491908</t>
+          <t>479136</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479908</t>
+          <t>466538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500489</t>
+          <t>488261</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>911864</t>
+          <t>949038</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>899267</t>
+          <t>936050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920874</t>
+          <t>959249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,32 +7371,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>37474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>32978</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>24992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36059</t>
+          <t>42845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>56749</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37669</t>
+          <t>43645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65107</t>
+          <t>71225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -7484,32 +7484,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>513389</t>
+          <t>597065</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502155</t>
+          <t>583363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521993</t>
+          <t>605898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>565115</t>
+          <t>590215</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>555943</t>
+          <t>580348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573954</t>
+          <t>598201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1078504</t>
+          <t>1187280</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1063233</t>
+          <t>1172804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090671</t>
+          <t>1200384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32783</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>23853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57045</t>
+          <t>62278</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44904</t>
+          <t>50387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69752</t>
+          <t>73565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>89829</t>
+          <t>96751</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56651</t>
+          <t>80825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116099</t>
+          <t>115590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>855003</t>
+          <t>666144</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836649</t>
+          <t>650872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873296</t>
+          <t>676764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>655836</t>
+          <t>674608</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>643129</t>
+          <t>663321</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>667977</t>
+          <t>686499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1510838</t>
+          <t>1340753</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1484568</t>
+          <t>1321914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1544016</t>
+          <t>1356679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>23906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43630</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>64234</t>
+          <t>71966</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53420</t>
+          <t>60686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75787</t>
+          <t>83940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>96477</t>
+          <t>105307</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80031</t>
+          <t>90725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112127</t>
+          <t>123860</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>528991</t>
+          <t>576006</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>517604</t>
+          <t>564650</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538075</t>
+          <t>585440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>483671</t>
+          <t>536889</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472118</t>
+          <t>524915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>494485</t>
+          <t>548169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1012662</t>
+          <t>1112895</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>997012</t>
+          <t>1094342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1029108</t>
+          <t>1127477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>36482</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67142</t>
+          <t>55522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>56873</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>47006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71841</t>
+          <t>68343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>356987</t>
+          <t>395455</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350607</t>
+          <t>388954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361501</t>
+          <t>400133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>567021</t>
+          <t>393918</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>541226</t>
+          <t>383644</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>591345</t>
+          <t>402684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>924009</t>
+          <t>789373</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>904692</t>
+          <t>777903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950445</t>
+          <t>799240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20998</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>51375</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37908</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>62785</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>56641</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73221</t>
+          <t>82162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>268456</t>
+          <t>293777</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>261761</t>
+          <t>286176</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273434</t>
+          <t>299716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>379459</t>
+          <t>413234</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>369534</t>
+          <t>401824</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387923</t>
+          <t>422485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>647914</t>
+          <t>707011</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635369</t>
+          <t>692645</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>658335</t>
+          <t>718166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95568</t>
+          <t>110878</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>151131</t>
+          <t>160747</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>268431</t>
+          <t>299330</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>217540</t>
+          <t>272183</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>301198</t>
+          <t>328950</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>394233</t>
+          <t>434548</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>345309</t>
+          <t>394765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>440752</t>
+          <t>470025</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3334015</t>
+          <t>3397544</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3308686</t>
+          <t>3372015</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3364249</t>
+          <t>3421884</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3443849</t>
+          <t>3437624</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3411082</t>
+          <t>3408004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3494740</t>
+          <t>3464771</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6777864</t>
+          <t>6835168</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6731345</t>
+          <t>6799691</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6826788</t>
+          <t>6874951</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
